--- a/tests/fixtures/15_annual_budget/15_annual_budget_pattern-from-claude.xlsx
+++ b/tests/fixtures/15_annual_budget/15_annual_budget_pattern-from-claude.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q92"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>summary_label</t>
         </is>
       </c>
       <c r="C75" s="5" t="n"/>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>summary_label</t>
+          <t>total_income_label</t>
         </is>
       </c>
       <c r="C76" s="5" t="n"/>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>summary.total_income</t>
         </is>
       </c>
       <c r="C77" s="5" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>total_income_label</t>
+          <t>total_expenses_label</t>
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>summary.total_income</t>
+          <t>summary.total_expenses</t>
         </is>
       </c>
       <c r="C79" s="5" t="n"/>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>total_expenses_label</t>
+          <t>balance_label</t>
         </is>
       </c>
       <c r="C80" s="5" t="n"/>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>summary.total_expenses</t>
+          <t>summary.balance</t>
         </is>
       </c>
       <c r="C81" s="5" t="n"/>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>balance_label</t>
+          <t>pct_spent_label</t>
         </is>
       </c>
       <c r="C82" s="5" t="n"/>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>summary.balance</t>
+          <t>summary.pct_income_spent</t>
         </is>
       </c>
       <c r="C83" s="5" t="n"/>
@@ -3149,459 +3149,405 @@
       <c r="Q83" s="5" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>pct_spent_label</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="n"/>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="5" t="n"/>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="n"/>
-      <c r="K84" s="5" t="n"/>
-      <c r="L84" s="5" t="n"/>
-      <c r="M84" s="5" t="n"/>
-      <c r="N84" s="5" t="n"/>
-      <c r="O84" s="5" t="n"/>
-      <c r="P84" s="5" t="n"/>
-      <c r="Q84" s="5" t="n"/>
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="6" t="n"/>
+      <c r="G84" s="6" t="n"/>
+      <c r="H84" s="6" t="n"/>
+      <c r="I84" s="6" t="n"/>
+      <c r="J84" s="6" t="n"/>
+      <c r="K84" s="6" t="n"/>
+      <c r="L84" s="6" t="n"/>
+      <c r="M84" s="6" t="n"/>
+      <c r="N84" s="6" t="n"/>
+      <c r="O84" s="6" t="n"/>
+      <c r="P84" s="6" t="n"/>
+      <c r="Q84" s="6" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>summary.pct_income_spent</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="n"/>
-      <c r="D85" s="5" t="n"/>
-      <c r="E85" s="5" t="n"/>
-      <c r="F85" s="5" t="n"/>
-      <c r="G85" s="5" t="n"/>
-      <c r="H85" s="5" t="n"/>
-      <c r="I85" s="5" t="n"/>
-      <c r="J85" s="5" t="n"/>
-      <c r="K85" s="5" t="n"/>
-      <c r="L85" s="5" t="n"/>
-      <c r="M85" s="5" t="n"/>
-      <c r="N85" s="5" t="n"/>
-      <c r="O85" s="5" t="n"/>
-      <c r="P85" s="5" t="n"/>
-      <c r="Q85" s="5" t="n"/>
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>income_item</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>income_jan</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>income_feb</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>income_mar</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>income_apr</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>income_may</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>income_jun</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>income_jul</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>income_aug</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>income_sep</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>income_oct</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>income_nov</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>income_dec</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>income_total</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>income_average</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+      <c r="A86" s="3" t="n"/>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>DATA:*</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>income.item</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>income.jan</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>income.feb</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>income.mar</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>income.apr</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>income.may</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>income.jun</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>income.jul</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>income.aug</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>income.sep</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>income.oct</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>income.nov</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="inlineStr">
+        <is>
+          <t>income.dec</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>income.total</t>
+        </is>
+      </c>
+      <c r="Q86" s="3" t="inlineStr">
+        <is>
+          <t>income.average</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="6" t="n"/>
-      <c r="D86" s="6" t="n"/>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="6" t="n"/>
-      <c r="G86" s="6" t="n"/>
-      <c r="H86" s="6" t="n"/>
-      <c r="I86" s="6" t="n"/>
-      <c r="J86" s="6" t="n"/>
-      <c r="K86" s="6" t="n"/>
-      <c r="L86" s="6" t="n"/>
-      <c r="M86" s="6" t="n"/>
-      <c r="N86" s="6" t="n"/>
-      <c r="O86" s="6" t="n"/>
-      <c r="P86" s="6" t="n"/>
-      <c r="Q86" s="6" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+      <c r="E87" s="6" t="n"/>
+      <c r="F87" s="6" t="n"/>
+      <c r="G87" s="6" t="n"/>
+      <c r="H87" s="6" t="n"/>
+      <c r="I87" s="6" t="n"/>
+      <c r="J87" s="6" t="n"/>
+      <c r="K87" s="6" t="n"/>
+      <c r="L87" s="6" t="n"/>
+      <c r="M87" s="6" t="n"/>
+      <c r="N87" s="6" t="n"/>
+      <c r="O87" s="6" t="n"/>
+      <c r="P87" s="6" t="n"/>
+      <c r="Q87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>income_item</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>income_jan</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>income_feb</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>income_mar</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>income_apr</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>income_may</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>income_jun</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>income_jul</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>income_aug</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>income_sep</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>income_oct</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>income_nov</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>income_dec</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>income_total</t>
-        </is>
-      </c>
-      <c r="Q87" s="2" t="inlineStr">
-        <is>
-          <t>income_average</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="n"/>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_item</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_jan</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_feb</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_mar</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_apr</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_may</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_jun</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_jul</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_aug</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_sep</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_oct</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_nov</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_dec</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_total</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>expenses_average</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n"/>
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>income.item</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>income.jan</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>income.feb</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>income.mar</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>income.apr</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>income.may</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t>income.jun</t>
-        </is>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>income.jul</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>income.aug</t>
-        </is>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
-        <is>
-          <t>income.sep</t>
-        </is>
-      </c>
-      <c r="M88" s="3" t="inlineStr">
-        <is>
-          <t>income.oct</t>
-        </is>
-      </c>
-      <c r="N88" s="3" t="inlineStr">
-        <is>
-          <t>income.nov</t>
-        </is>
-      </c>
-      <c r="O88" s="3" t="inlineStr">
-        <is>
-          <t>income.dec</t>
-        </is>
-      </c>
-      <c r="P88" s="3" t="inlineStr">
-        <is>
-          <t>income.total</t>
-        </is>
-      </c>
-      <c r="Q88" s="3" t="inlineStr">
-        <is>
-          <t>income.average</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="n"/>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="6" t="n"/>
-      <c r="G89" s="6" t="n"/>
-      <c r="H89" s="6" t="n"/>
-      <c r="I89" s="6" t="n"/>
-      <c r="J89" s="6" t="n"/>
-      <c r="K89" s="6" t="n"/>
-      <c r="L89" s="6" t="n"/>
-      <c r="M89" s="6" t="n"/>
-      <c r="N89" s="6" t="n"/>
-      <c r="O89" s="6" t="n"/>
-      <c r="P89" s="6" t="n"/>
-      <c r="Q89" s="6" t="n"/>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.item</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.jan</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.feb</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.mar</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.apr</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.may</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.jun</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.jul</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.aug</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.sep</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.oct</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.nov</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.dec</t>
+        </is>
+      </c>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.total</t>
+        </is>
+      </c>
+      <c r="Q89" s="3" t="inlineStr">
+        <is>
+          <t>expenses.average</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n"/>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_item</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_jan</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_feb</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_mar</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_apr</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_may</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_jun</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_jul</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_aug</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_sep</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_oct</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_nov</t>
-        </is>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_dec</t>
-        </is>
-      </c>
-      <c r="P90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_total</t>
-        </is>
-      </c>
-      <c r="Q90" s="2" t="inlineStr">
-        <is>
-          <t>expenses_average</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="n"/>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>DATA:*</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.item</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.jan</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.feb</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.mar</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.apr</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.may</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.jun</t>
-        </is>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.jul</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.aug</t>
-        </is>
-      </c>
-      <c r="L91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.sep</t>
-        </is>
-      </c>
-      <c r="M91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.oct</t>
-        </is>
-      </c>
-      <c r="N91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.nov</t>
-        </is>
-      </c>
-      <c r="O91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.dec</t>
-        </is>
-      </c>
-      <c r="P91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.total</t>
-        </is>
-      </c>
-      <c r="Q91" s="3" t="inlineStr">
-        <is>
-          <t>expenses.average</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B92" s="4" t="n"/>
-      <c r="C92" s="4" t="n"/>
-      <c r="D92" s="4" t="n"/>
-      <c r="E92" s="4" t="n"/>
-      <c r="F92" s="4" t="n"/>
-      <c r="G92" s="4" t="n"/>
-      <c r="H92" s="4" t="n"/>
-      <c r="I92" s="4" t="n"/>
-      <c r="J92" s="4" t="n"/>
-      <c r="K92" s="4" t="n"/>
-      <c r="L92" s="4" t="n"/>
-      <c r="M92" s="4" t="n"/>
-      <c r="N92" s="4" t="n"/>
-      <c r="O92" s="4" t="n"/>
-      <c r="P92" s="4" t="n"/>
-      <c r="Q92" s="4" t="n"/>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="n"/>
+      <c r="E90" s="4" t="n"/>
+      <c r="F90" s="4" t="n"/>
+      <c r="G90" s="4" t="n"/>
+      <c r="H90" s="4" t="n"/>
+      <c r="I90" s="4" t="n"/>
+      <c r="J90" s="4" t="n"/>
+      <c r="K90" s="4" t="n"/>
+      <c r="L90" s="4" t="n"/>
+      <c r="M90" s="4" t="n"/>
+      <c r="N90" s="4" t="n"/>
+      <c r="O90" s="4" t="n"/>
+      <c r="P90" s="4" t="n"/>
+      <c r="Q90" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
